--- a/Analysis/exports/consolidated_history.xlsx
+++ b/Analysis/exports/consolidated_history.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>NYKAA</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>AUBANK</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>DIXON</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>GRASIM</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>NMDC</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>MCX</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>CAMS</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>RBLBANK</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>GAIL</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>NMDC</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>SBIN</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>SBIN</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>PNB</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>RBLBANK</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
     </row>

--- a/Analysis/exports/consolidated_history.xlsx
+++ b/Analysis/exports/consolidated_history.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Probable Upside" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Support Entry" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Consolidation Breakout" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Probable Upside" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support Entry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation Breakout" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>NYKAA</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>GRASIM</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>AUBANK</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>BHEL</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>PAYTM</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>DIXON</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>TITAN</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>CAMS</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>YESBANK</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>KFINTECH</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>INDIGO</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>GAIL</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>NMDC</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>RBLBANK</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>RBLBANK</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>TITAN</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>PNB</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>360ONE</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>LT</t>
         </is>
       </c>
     </row>

--- a/Analysis/exports/consolidated_history.xlsx
+++ b/Analysis/exports/consolidated_history.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Probable Upside" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support Entry" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation Breakout" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Probable Upside" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Support Entry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consolidation Breakout" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>NYKAA</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>AUBANK</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>DIXON</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>GRASIM</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>NMDC</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>MCX</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>CAMS</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>OIL</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>RBLBANK</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>GAIL</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>NMDC</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>INDIGO</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>SBIN</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>SBIN</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>360ONE</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>PNB</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>TITAN</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>RBLBANK</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
     </row>

--- a/Analysis/exports/consolidated_history.xlsx
+++ b/Analysis/exports/consolidated_history.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,9 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <sz val="10"/>
     </font>
   </fonts>
@@ -81,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -90,6 +93,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -458,11 +464,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -476,6 +484,16 @@
           <t>2026-08-31</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -488,6 +506,16 @@
           <t>AUROPHARMA</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -500,6 +528,16 @@
           <t>NYKAA</t>
         </is>
       </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -512,6 +550,16 @@
           <t>AUBANK</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -524,6 +572,16 @@
           <t>SOLARINDS</t>
         </is>
       </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -536,6 +594,16 @@
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -548,6 +616,16 @@
           <t>BOSCHLTD</t>
         </is>
       </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -560,6 +638,16 @@
           <t>DIXON</t>
         </is>
       </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -572,6 +660,16 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -584,6 +682,16 @@
           <t>GRASIM</t>
         </is>
       </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -596,6 +704,16 @@
           <t>JINDALSTEL</t>
         </is>
       </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -608,6 +726,16 @@
           <t>DLF</t>
         </is>
       </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -620,6 +748,16 @@
           <t>NMDC</t>
         </is>
       </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -632,6 +770,16 @@
           <t>UNOMINDA</t>
         </is>
       </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -644,6 +792,16 @@
           <t>ZYDUSLIFE</t>
         </is>
       </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -656,6 +814,16 @@
           <t>MCX</t>
         </is>
       </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -668,6 +836,16 @@
           <t>HYUNDAI</t>
         </is>
       </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -680,6 +858,16 @@
           <t>ICICIBANK</t>
         </is>
       </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -692,6 +880,16 @@
           <t>LAURUSLABS</t>
         </is>
       </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -704,6 +902,16 @@
           <t>ATHERENERG</t>
         </is>
       </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -714,6 +922,16 @@
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
         </is>
       </c>
     </row>
@@ -729,11 +947,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -747,6 +967,16 @@
           <t>2026-08-31</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -759,6 +989,16 @@
           <t>CAMS</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -771,6 +1011,16 @@
           <t>SONACOMS</t>
         </is>
       </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -783,6 +1033,16 @@
           <t>OIL</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -795,6 +1055,16 @@
           <t>PIDILITIND</t>
         </is>
       </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -807,6 +1077,16 @@
           <t>RBLBANK</t>
         </is>
       </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -819,6 +1099,16 @@
           <t>OBEROIRLTY</t>
         </is>
       </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -831,6 +1121,16 @@
           <t>DELHIVERY</t>
         </is>
       </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -843,6 +1143,16 @@
           <t>M&amp;M</t>
         </is>
       </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -855,6 +1165,16 @@
           <t>GAIL</t>
         </is>
       </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -867,6 +1187,16 @@
           <t>NMDC</t>
         </is>
       </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -879,6 +1209,16 @@
           <t>INDIGO</t>
         </is>
       </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -891,6 +1231,16 @@
           <t>TECHM</t>
         </is>
       </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -903,6 +1253,16 @@
           <t>INDHOTEL</t>
         </is>
       </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -915,6 +1275,16 @@
           <t>SBIN</t>
         </is>
       </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -927,6 +1297,16 @@
           <t>MPHASIS</t>
         </is>
       </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -939,6 +1319,16 @@
           <t>PHOENIXLTD</t>
         </is>
       </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -951,6 +1341,16 @@
           <t>BHARATFORG</t>
         </is>
       </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -963,6 +1363,16 @@
           <t>NESTLEIND</t>
         </is>
       </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -975,6 +1385,16 @@
           <t>ASHOKLEY</t>
         </is>
       </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -985,6 +1405,16 @@
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
         </is>
       </c>
     </row>
@@ -1000,11 +1430,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1018,6 +1450,16 @@
           <t>2026-08-31</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1030,6 +1472,16 @@
           <t>BAJAJFINSV</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1042,6 +1494,16 @@
           <t>M&amp;M</t>
         </is>
       </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1054,6 +1516,16 @@
           <t>BAJFINANCE</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1066,6 +1538,16 @@
           <t>CHOLAFIN</t>
         </is>
       </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1078,6 +1560,16 @@
           <t>SBIN</t>
         </is>
       </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1090,6 +1582,16 @@
           <t>DLF</t>
         </is>
       </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1102,6 +1604,16 @@
           <t>MOTHERSON</t>
         </is>
       </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1114,6 +1626,16 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1126,6 +1648,16 @@
           <t>UNOMINDA</t>
         </is>
       </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1138,6 +1670,16 @@
           <t>360ONE</t>
         </is>
       </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1150,6 +1692,16 @@
           <t>SONACOMS</t>
         </is>
       </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1162,6 +1714,12 @@
           <t>PNB</t>
         </is>
       </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1174,6 +1732,8 @@
           <t>SUNPHARMA</t>
         </is>
       </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1186,6 +1746,8 @@
           <t>TITAN</t>
         </is>
       </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1198,6 +1760,8 @@
           <t>TVSMOTOR</t>
         </is>
       </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1210,6 +1774,8 @@
           <t>RBLBANK</t>
         </is>
       </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1222,6 +1788,8 @@
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1234,6 +1802,8 @@
           <t>PIDILITIND</t>
         </is>
       </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1246,6 +1816,8 @@
           <t>APOLLOHOSP</t>
         </is>
       </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1258,6 +1830,8 @@
           <t>TORNTPHARM</t>
         </is>
       </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Analysis/exports/consolidated_history.xlsx
+++ b/Analysis/exports/consolidated_history.xlsx
@@ -464,13 +464,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -494,6 +495,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -516,6 +522,11 @@
           <t>DIVISLAB</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -538,6 +549,11 @@
           <t>OIL</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -560,6 +576,11 @@
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -582,6 +603,11 @@
           <t>POLICYBZR</t>
         </is>
       </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -604,6 +630,11 @@
           <t>GAIL</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -626,6 +657,11 @@
           <t>COFORGE</t>
         </is>
       </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -648,6 +684,11 @@
           <t>TECHM</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -670,6 +711,11 @@
           <t>DLF</t>
         </is>
       </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -692,6 +738,11 @@
           <t>AUROPHARMA</t>
         </is>
       </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -714,6 +765,11 @@
           <t>GRASIM</t>
         </is>
       </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -736,6 +792,11 @@
           <t>BHEL</t>
         </is>
       </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -758,6 +819,11 @@
           <t>OFSS</t>
         </is>
       </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -780,6 +846,11 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -802,6 +873,11 @@
           <t>ATHERENERG</t>
         </is>
       </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -824,6 +900,11 @@
           <t>IDFCFIRSTB</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -846,6 +927,7 @@
           <t>CGPOWER</t>
         </is>
       </c>
+      <c r="E17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -868,6 +950,7 @@
           <t>TORNTPHARM</t>
         </is>
       </c>
+      <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -890,6 +973,7 @@
           <t>KALYANKJIL</t>
         </is>
       </c>
+      <c r="E19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -912,6 +996,7 @@
           <t>CDSL</t>
         </is>
       </c>
+      <c r="E20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -934,6 +1019,7 @@
           <t>UNIONBANK</t>
         </is>
       </c>
+      <c r="E21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -947,13 +1033,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -977,6 +1064,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -999,6 +1091,11 @@
           <t>PAGEIND</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1021,6 +1118,11 @@
           <t>CDSL</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1043,6 +1145,11 @@
           <t>HINDZINC</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1065,6 +1172,11 @@
           <t>MAZDOCK</t>
         </is>
       </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1087,6 +1199,11 @@
           <t>NESTLEIND</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1109,6 +1226,11 @@
           <t>NMDC</t>
         </is>
       </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1131,6 +1253,11 @@
           <t>APOLLOHOSP</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1153,6 +1280,11 @@
           <t>CIPLA</t>
         </is>
       </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1175,6 +1307,11 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1197,6 +1334,11 @@
           <t>ADANIENT</t>
         </is>
       </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1219,6 +1361,11 @@
           <t>AMBER</t>
         </is>
       </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1241,6 +1388,11 @@
           <t>DELHIVERY</t>
         </is>
       </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1263,6 +1415,11 @@
           <t>BSE</t>
         </is>
       </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1285,6 +1442,11 @@
           <t>ADANIGREEN</t>
         </is>
       </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1307,6 +1469,11 @@
           <t>PGEL</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1329,6 +1496,7 @@
           <t>NATIONALUM</t>
         </is>
       </c>
+      <c r="E17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1351,6 +1519,7 @@
           <t>MANAPPURAM</t>
         </is>
       </c>
+      <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1373,6 +1542,7 @@
           <t>GODREJPROP</t>
         </is>
       </c>
+      <c r="E19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1395,6 +1565,7 @@
           <t>PETRONET</t>
         </is>
       </c>
+      <c r="E20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1417,6 +1588,7 @@
           <t>TITAN</t>
         </is>
       </c>
+      <c r="E21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1430,13 +1602,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1460,6 +1633,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1482,6 +1660,11 @@
           <t>TITAN</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1504,6 +1687,11 @@
           <t>BAJAJFINSV</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,6 +1714,11 @@
           <t>RADICO</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1548,6 +1741,11 @@
           <t>CHOLAFIN</t>
         </is>
       </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1570,6 +1768,11 @@
           <t>PNB</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1592,6 +1795,11 @@
           <t>ABB</t>
         </is>
       </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1614,6 +1822,11 @@
           <t>SIEMENS</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1636,6 +1849,11 @@
           <t>UNOMINDA</t>
         </is>
       </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1658,6 +1876,11 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1680,6 +1903,7 @@
           <t>ETERNAL</t>
         </is>
       </c>
+      <c r="E11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1702,6 +1926,7 @@
           <t>NAUKRI</t>
         </is>
       </c>
+      <c r="E12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1720,6 +1945,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1734,6 +1960,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1748,6 +1975,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1762,6 +1990,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr"/>
       <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1776,6 +2005,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1790,6 +2020,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1804,6 +2035,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1818,6 +2050,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1832,6 +2065,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Analysis/exports/consolidated_history.xlsx
+++ b/Analysis/exports/consolidated_history.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -500,6 +501,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -527,6 +533,11 @@
           <t>GAIL</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -554,6 +565,11 @@
           <t>AUROPHARMA</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -581,6 +597,11 @@
           <t>DIVISLAB</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -608,6 +629,11 @@
           <t>GRASIM</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -635,6 +661,11 @@
           <t>ICICIBANK</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -662,6 +693,11 @@
           <t>COFORGE</t>
         </is>
       </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -689,6 +725,11 @@
           <t>CDSL</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -716,6 +757,11 @@
           <t>COALINDIA</t>
         </is>
       </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -743,6 +789,11 @@
           <t>SAIL</t>
         </is>
       </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -770,6 +821,11 @@
           <t>SOLARINDS</t>
         </is>
       </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -797,6 +853,11 @@
           <t>UNIONBANK</t>
         </is>
       </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -824,6 +885,11 @@
           <t>ZYDUSLIFE</t>
         </is>
       </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -851,6 +917,11 @@
           <t>OIL</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -878,6 +949,11 @@
           <t>APLAPOLLO</t>
         </is>
       </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -905,6 +981,11 @@
           <t>OFSS</t>
         </is>
       </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -928,6 +1009,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -951,6 +1033,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -974,6 +1057,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -997,6 +1081,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1020,6 +1105,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1033,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1041,6 +1127,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1069,6 +1156,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1096,6 +1188,11 @@
           <t>LAURUSLABS</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1123,6 +1220,11 @@
           <t>GVT&amp;D</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1150,6 +1252,11 @@
           <t>DELHIVERY</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1177,6 +1284,11 @@
           <t>ADANIENT</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1204,6 +1316,11 @@
           <t>LT</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1231,6 +1348,11 @@
           <t>ABB</t>
         </is>
       </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1258,6 +1380,11 @@
           <t>CONCOR</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1285,6 +1412,11 @@
           <t>CHOLAFIN</t>
         </is>
       </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1312,6 +1444,11 @@
           <t>PETRONET</t>
         </is>
       </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1339,6 +1476,11 @@
           <t>JINDALSTEL</t>
         </is>
       </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1366,6 +1508,11 @@
           <t>TORNTPHARM</t>
         </is>
       </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1393,6 +1540,11 @@
           <t>PGEL</t>
         </is>
       </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1420,6 +1572,11 @@
           <t>LODHA</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1447,6 +1604,11 @@
           <t>AMBER</t>
         </is>
       </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1474,6 +1636,11 @@
           <t>HYUNDAI</t>
         </is>
       </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1497,6 +1664,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1520,6 +1688,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1543,6 +1712,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1566,6 +1736,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1589,6 +1760,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1602,7 +1774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1610,6 +1782,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1638,6 +1811,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1665,6 +1843,11 @@
           <t>ETERNAL</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1692,6 +1875,11 @@
           <t>CHOLAFIN</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1719,6 +1907,11 @@
           <t>JSWSTEEL</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1746,6 +1939,11 @@
           <t>PNB</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1773,6 +1971,11 @@
           <t>TITAN</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1800,6 +2003,7 @@
           <t>ABB</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1827,6 +2031,7 @@
           <t>UNOMINDA</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1854,6 +2059,7 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1881,6 +2087,7 @@
           <t>UNIONBANK</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1904,6 +2111,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1927,6 +2135,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1946,6 +2155,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1961,6 +2171,7 @@
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1976,6 +2187,7 @@
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1991,6 +2203,7 @@
       <c r="C16" s="4" t="inlineStr"/>
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2006,6 +2219,7 @@
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2021,6 +2235,7 @@
       <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -2036,6 +2251,7 @@
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2051,6 +2267,7 @@
       <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -2066,6 +2283,7 @@
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
